--- a/output/yearly_population_iteration_3_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_3_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5534</v>
+        <v>5844</v>
       </c>
       <c r="C2" t="n">
-        <v>10265</v>
+        <v>9115</v>
       </c>
       <c r="D2" t="n">
-        <v>19111</v>
+        <v>33321</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3616</v>
+        <v>3320</v>
       </c>
       <c r="C3" t="n">
-        <v>6852</v>
+        <v>3631</v>
       </c>
       <c r="D3" t="n">
-        <v>12338</v>
+        <v>18585</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3005</v>
+        <v>2567</v>
       </c>
       <c r="C4" t="n">
-        <v>8143</v>
+        <v>4422</v>
       </c>
       <c r="D4" t="n">
-        <v>5861</v>
+        <v>9691</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2000</v>
+        <v>1671</v>
       </c>
       <c r="C5" t="n">
-        <v>6054</v>
+        <v>4338</v>
       </c>
       <c r="D5" t="n">
-        <v>2299</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1138</v>
+        <v>901</v>
       </c>
       <c r="C6" t="n">
-        <v>3287</v>
+        <v>3376</v>
       </c>
       <c r="D6" t="n">
-        <v>1070</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>534</v>
+        <v>421</v>
       </c>
       <c r="C7" t="n">
-        <v>1658</v>
+        <v>2090</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="C8" t="n">
-        <v>747</v>
+        <v>1009</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>327</v>
+        <v>425</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
         <v>161</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8331</v>
+        <v>6495</v>
       </c>
       <c r="C2" t="n">
-        <v>12695</v>
+        <v>11691</v>
       </c>
       <c r="D2" t="n">
-        <v>20854</v>
+        <v>34695</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3632</v>
+        <v>3567</v>
       </c>
       <c r="C3" t="n">
-        <v>7378</v>
+        <v>5312</v>
       </c>
       <c r="D3" t="n">
-        <v>12430</v>
+        <v>19252</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2799</v>
+        <v>2465</v>
       </c>
       <c r="C4" t="n">
-        <v>7288</v>
+        <v>3923</v>
       </c>
       <c r="D4" t="n">
-        <v>6739</v>
+        <v>10669</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2169</v>
+        <v>1810</v>
       </c>
       <c r="C5" t="n">
-        <v>6890</v>
+        <v>4285</v>
       </c>
       <c r="D5" t="n">
-        <v>2754</v>
+        <v>4425</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1364</v>
+        <v>1119</v>
       </c>
       <c r="C6" t="n">
-        <v>4445</v>
+        <v>3726</v>
       </c>
       <c r="D6" t="n">
-        <v>1244</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>704</v>
+        <v>552</v>
       </c>
       <c r="C7" t="n">
-        <v>2375</v>
+        <v>2643</v>
       </c>
       <c r="D7" t="n">
-        <v>697</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>292</v>
+        <v>231</v>
       </c>
       <c r="C8" t="n">
-        <v>1123</v>
+        <v>1443</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C9" t="n">
-        <v>499</v>
+        <v>655</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8227</v>
+        <v>6862</v>
       </c>
       <c r="C2" t="n">
-        <v>10703</v>
+        <v>11962</v>
       </c>
       <c r="D2" t="n">
-        <v>31878</v>
+        <v>39932</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4415</v>
+        <v>3837</v>
       </c>
       <c r="C3" t="n">
-        <v>8536</v>
+        <v>6970</v>
       </c>
       <c r="D3" t="n">
-        <v>12645</v>
+        <v>19873</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2671</v>
+        <v>2489</v>
       </c>
       <c r="C4" t="n">
-        <v>7104</v>
+        <v>4390</v>
       </c>
       <c r="D4" t="n">
-        <v>7288</v>
+        <v>11478</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2161</v>
+        <v>1838</v>
       </c>
       <c r="C5" t="n">
-        <v>6844</v>
+        <v>4046</v>
       </c>
       <c r="D5" t="n">
-        <v>3244</v>
+        <v>5189</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1533</v>
+        <v>1261</v>
       </c>
       <c r="C6" t="n">
-        <v>5391</v>
+        <v>3877</v>
       </c>
       <c r="D6" t="n">
-        <v>1418</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>870</v>
+        <v>688</v>
       </c>
       <c r="C7" t="n">
-        <v>3162</v>
+        <v>3040</v>
       </c>
       <c r="D7" t="n">
-        <v>764</v>
+        <v>871</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>394</v>
+        <v>310</v>
       </c>
       <c r="C8" t="n">
-        <v>1590</v>
+        <v>1901</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="C9" t="n">
-        <v>731</v>
+        <v>934</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>337</v>
+        <v>422</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7606</v>
+        <v>6379</v>
       </c>
       <c r="C2" t="n">
-        <v>7449</v>
+        <v>8325</v>
       </c>
       <c r="D2" t="n">
-        <v>26109</v>
+        <v>32899</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5021</v>
+        <v>4507</v>
       </c>
       <c r="C3" t="n">
-        <v>12308</v>
+        <v>9789</v>
       </c>
       <c r="D3" t="n">
-        <v>13771</v>
+        <v>21650</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1996</v>
+        <v>1698</v>
       </c>
       <c r="C4" t="n">
-        <v>10389</v>
+        <v>6244</v>
       </c>
       <c r="D4" t="n">
-        <v>6999</v>
+        <v>11079</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1416</v>
+        <v>1165</v>
       </c>
       <c r="C5" t="n">
-        <v>5283</v>
+        <v>3799</v>
       </c>
       <c r="D5" t="n">
-        <v>2261</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>803</v>
+        <v>635</v>
       </c>
       <c r="C6" t="n">
-        <v>3098</v>
+        <v>2979</v>
       </c>
       <c r="D6" t="n">
-        <v>748</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>364</v>
+        <v>286</v>
       </c>
       <c r="C7" t="n">
-        <v>1558</v>
+        <v>1862</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>716</v>
+        <v>915</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>330</v>
+        <v>413</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4661</v>
+        <v>3870</v>
       </c>
       <c r="C2" t="n">
-        <v>3798</v>
+        <v>4400</v>
       </c>
       <c r="D2" t="n">
-        <v>18374</v>
+        <v>22398</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5257</v>
+        <v>4563</v>
       </c>
       <c r="C3" t="n">
-        <v>9183</v>
+        <v>8310</v>
       </c>
       <c r="D3" t="n">
-        <v>14787</v>
+        <v>22140</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2746</v>
+        <v>2366</v>
       </c>
       <c r="C4" t="n">
-        <v>11456</v>
+        <v>7953</v>
       </c>
       <c r="D4" t="n">
-        <v>7828</v>
+        <v>12370</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1546</v>
+        <v>1294</v>
       </c>
       <c r="C5" t="n">
-        <v>7485</v>
+        <v>4828</v>
       </c>
       <c r="D5" t="n">
-        <v>2826</v>
+        <v>4287</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>952</v>
+        <v>747</v>
       </c>
       <c r="C6" t="n">
-        <v>3991</v>
+        <v>3436</v>
       </c>
       <c r="D6" t="n">
-        <v>906</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>269</v>
       </c>
       <c r="C7" t="n">
-        <v>2102</v>
+        <v>2291</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>950</v>
+        <v>1207</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>375</v>
+        <v>447</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
         <v>166</v>
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4415</v>
+        <v>4655</v>
       </c>
       <c r="C2" t="n">
-        <v>7357</v>
+        <v>10773</v>
       </c>
       <c r="D2" t="n">
-        <v>18605</v>
+        <v>20868</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4208</v>
+        <v>3632</v>
       </c>
       <c r="C3" t="n">
-        <v>5957</v>
+        <v>5748</v>
       </c>
       <c r="D3" t="n">
-        <v>14281</v>
+        <v>20687</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3286</v>
+        <v>2804</v>
       </c>
       <c r="C4" t="n">
-        <v>10126</v>
+        <v>7958</v>
       </c>
       <c r="D4" t="n">
-        <v>8725</v>
+        <v>13588</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1817</v>
+        <v>1543</v>
       </c>
       <c r="C5" t="n">
-        <v>9159</v>
+        <v>6213</v>
       </c>
       <c r="D5" t="n">
-        <v>3508</v>
+        <v>5398</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1098</v>
+        <v>887</v>
       </c>
       <c r="C6" t="n">
-        <v>5534</v>
+        <v>4005</v>
       </c>
       <c r="D6" t="n">
-        <v>1170</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>507</v>
+        <v>399</v>
       </c>
       <c r="C7" t="n">
-        <v>2917</v>
+        <v>2795</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="C8" t="n">
-        <v>1410</v>
+        <v>1643</v>
       </c>
       <c r="D8" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>587</v>
+        <v>726</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2672</v>
+        <v>2775</v>
       </c>
       <c r="C2" t="n">
-        <v>3524</v>
+        <v>5132</v>
       </c>
       <c r="D2" t="n">
-        <v>12995</v>
+        <v>14539</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4143</v>
+        <v>3734</v>
       </c>
       <c r="C3" t="n">
-        <v>6244</v>
+        <v>7230</v>
       </c>
       <c r="D3" t="n">
-        <v>14410</v>
+        <v>20242</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3582</v>
+        <v>3090</v>
       </c>
       <c r="C4" t="n">
-        <v>9566</v>
+        <v>7856</v>
       </c>
       <c r="D4" t="n">
-        <v>9392</v>
+        <v>14492</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1904</v>
+        <v>1593</v>
       </c>
       <c r="C5" t="n">
-        <v>10861</v>
+        <v>7604</v>
       </c>
       <c r="D5" t="n">
-        <v>3711</v>
+        <v>5686</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>904</v>
+        <v>721</v>
       </c>
       <c r="C6" t="n">
-        <v>6367</v>
+        <v>4792</v>
       </c>
       <c r="D6" t="n">
-        <v>1158</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="C7" t="n">
-        <v>2853</v>
+        <v>2962</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>989</v>
+        <v>1194</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3043</v>
+        <v>3323</v>
       </c>
       <c r="C2" t="n">
-        <v>7485</v>
+        <v>9054</v>
       </c>
       <c r="D2" t="n">
-        <v>14225</v>
+        <v>14949</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3043</v>
+        <v>2860</v>
       </c>
       <c r="C3" t="n">
-        <v>4498</v>
+        <v>5620</v>
       </c>
       <c r="D3" t="n">
-        <v>13283</v>
+        <v>18184</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3325</v>
+        <v>2920</v>
       </c>
       <c r="C4" t="n">
-        <v>7928</v>
+        <v>7479</v>
       </c>
       <c r="D4" t="n">
-        <v>9877</v>
+        <v>14934</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2282</v>
+        <v>1937</v>
       </c>
       <c r="C5" t="n">
-        <v>10179</v>
+        <v>7627</v>
       </c>
       <c r="D5" t="n">
-        <v>4416</v>
+        <v>6781</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1163</v>
+        <v>949</v>
       </c>
       <c r="C6" t="n">
-        <v>8185</v>
+        <v>5930</v>
       </c>
       <c r="D6" t="n">
-        <v>1497</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>331</v>
+        <v>265</v>
       </c>
       <c r="C7" t="n">
-        <v>4222</v>
+        <v>3689</v>
       </c>
       <c r="D7" t="n">
-        <v>631</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>1675</v>
+        <v>1840</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>492</v>
+        <v>589</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
         <v>174</v>
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>58</v>
+      </c>
+      <c r="D13" t="n">
         <v>59</v>
-      </c>
-      <c r="D13" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2307</v>
+        <v>2188</v>
       </c>
       <c r="C2" t="n">
-        <v>4241</v>
+        <v>5178</v>
       </c>
       <c r="D2" t="n">
-        <v>10067</v>
+        <v>12136</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2668</v>
+        <v>2633</v>
       </c>
       <c r="C3" t="n">
-        <v>5165</v>
+        <v>6297</v>
       </c>
       <c r="D3" t="n">
-        <v>12687</v>
+        <v>16861</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2989</v>
+        <v>2672</v>
       </c>
       <c r="C4" t="n">
-        <v>6598</v>
+        <v>6807</v>
       </c>
       <c r="D4" t="n">
-        <v>10096</v>
+        <v>15028</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2471</v>
+        <v>2097</v>
       </c>
       <c r="C5" t="n">
-        <v>9580</v>
+        <v>7710</v>
       </c>
       <c r="D5" t="n">
-        <v>4943</v>
+        <v>7566</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1334</v>
+        <v>1113</v>
       </c>
       <c r="C6" t="n">
-        <v>9107</v>
+        <v>6671</v>
       </c>
       <c r="D6" t="n">
-        <v>1732</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>238</v>
       </c>
       <c r="C7" t="n">
-        <v>5403</v>
+        <v>4409</v>
       </c>
       <c r="D7" t="n">
-        <v>697</v>
+        <v>774</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>2200</v>
+        <v>2326</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>549</v>
+        <v>646</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3140</v>
+        <v>2418</v>
       </c>
       <c r="C2" t="n">
-        <v>6735</v>
+        <v>7832</v>
       </c>
       <c r="D2" t="n">
-        <v>10299</v>
+        <v>13925</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2146</v>
+        <v>2088</v>
       </c>
       <c r="C3" t="n">
-        <v>4334</v>
+        <v>5226</v>
       </c>
       <c r="D3" t="n">
-        <v>11682</v>
+        <v>15376</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2504</v>
+        <v>2333</v>
       </c>
       <c r="C4" t="n">
-        <v>5882</v>
+        <v>6454</v>
       </c>
       <c r="D4" t="n">
-        <v>10040</v>
+        <v>14673</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2413</v>
+        <v>2084</v>
       </c>
       <c r="C5" t="n">
-        <v>8235</v>
+        <v>7194</v>
       </c>
       <c r="D5" t="n">
-        <v>5485</v>
+        <v>8338</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1584</v>
+        <v>1332</v>
       </c>
       <c r="C6" t="n">
-        <v>9206</v>
+        <v>7005</v>
       </c>
       <c r="D6" t="n">
-        <v>2110</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>540</v>
+        <v>444</v>
       </c>
       <c r="C7" t="n">
-        <v>6707</v>
+        <v>5270</v>
       </c>
       <c r="D7" t="n">
-        <v>811</v>
+        <v>959</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C8" t="n">
-        <v>3266</v>
+        <v>3019</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1071</v>
+        <v>1178</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3725,7 +3725,7 @@
         <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5857</v>
+        <v>4856</v>
       </c>
       <c r="C2" t="n">
-        <v>5352</v>
+        <v>10732</v>
       </c>
       <c r="D2" t="n">
-        <v>9064</v>
+        <v>11743</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2297</v>
+        <v>1749</v>
       </c>
       <c r="C2" t="n">
-        <v>3933</v>
+        <v>4573</v>
       </c>
       <c r="D2" t="n">
-        <v>7662</v>
+        <v>10360</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2886</v>
+        <v>2747</v>
       </c>
       <c r="C3" t="n">
-        <v>5297</v>
+        <v>6257</v>
       </c>
       <c r="D3" t="n">
-        <v>12562</v>
+        <v>16526</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3508</v>
+        <v>3099</v>
       </c>
       <c r="C4" t="n">
-        <v>8652</v>
+        <v>8995</v>
       </c>
       <c r="D4" t="n">
-        <v>10183</v>
+        <v>15101</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1485</v>
+        <v>1269</v>
       </c>
       <c r="C5" t="n">
-        <v>12615</v>
+        <v>10187</v>
       </c>
       <c r="D5" t="n">
-        <v>5003</v>
+        <v>7516</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>498</v>
+        <v>410</v>
       </c>
       <c r="C6" t="n">
-        <v>8196</v>
+        <v>6400</v>
       </c>
       <c r="D6" t="n">
-        <v>1704</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C7" t="n">
-        <v>3200</v>
+        <v>2958</v>
       </c>
       <c r="D7" t="n">
-        <v>532</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1049</v>
+        <v>1154</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4333,7 +4333,7 @@
         <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7099</v>
+        <v>6650</v>
       </c>
       <c r="C2" t="n">
-        <v>3793</v>
+        <v>5966</v>
       </c>
       <c r="D2" t="n">
-        <v>14033</v>
+        <v>23791</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2488</v>
+        <v>2064</v>
       </c>
       <c r="C3" t="n">
-        <v>2697</v>
+        <v>5408</v>
       </c>
       <c r="D3" t="n">
-        <v>2162</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6383</v>
+        <v>4350</v>
       </c>
       <c r="C2" t="n">
-        <v>9810</v>
+        <v>5738</v>
       </c>
       <c r="D2" t="n">
-        <v>14299</v>
+        <v>36720</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3935</v>
+        <v>3574</v>
       </c>
       <c r="C3" t="n">
-        <v>2865</v>
+        <v>4936</v>
       </c>
       <c r="D3" t="n">
-        <v>3997</v>
+        <v>5977</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1114</v>
+        <v>931</v>
       </c>
       <c r="C4" t="n">
-        <v>1649</v>
+        <v>3212</v>
       </c>
       <c r="D4" t="n">
-        <v>1617</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5861</v>
+        <v>4189</v>
       </c>
       <c r="C2" t="n">
-        <v>5021</v>
+        <v>8750</v>
       </c>
       <c r="D2" t="n">
-        <v>14704</v>
+        <v>36812</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4211</v>
+        <v>3253</v>
       </c>
       <c r="C3" t="n">
-        <v>5757</v>
+        <v>4652</v>
       </c>
       <c r="D3" t="n">
-        <v>5357</v>
+        <v>10465</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2136</v>
+        <v>1882</v>
       </c>
       <c r="C4" t="n">
-        <v>2303</v>
+        <v>4105</v>
       </c>
       <c r="D4" t="n">
-        <v>2024</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>517</v>
+        <v>436</v>
       </c>
       <c r="C5" t="n">
-        <v>995</v>
+        <v>1823</v>
       </c>
       <c r="D5" t="n">
-        <v>1217</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5776</v>
+        <v>5903</v>
       </c>
       <c r="C2" t="n">
-        <v>12461</v>
+        <v>7391</v>
       </c>
       <c r="D2" t="n">
-        <v>21406</v>
+        <v>32754</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4105</v>
+        <v>3038</v>
       </c>
       <c r="C3" t="n">
-        <v>4666</v>
+        <v>5859</v>
       </c>
       <c r="D3" t="n">
-        <v>6400</v>
+        <v>13733</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2668</v>
+        <v>2172</v>
       </c>
       <c r="C4" t="n">
-        <v>4145</v>
+        <v>4308</v>
       </c>
       <c r="D4" t="n">
-        <v>2550</v>
+        <v>3856</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1104</v>
+        <v>935</v>
       </c>
       <c r="C5" t="n">
-        <v>1664</v>
+        <v>2928</v>
       </c>
       <c r="D5" t="n">
-        <v>1327</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="C6" t="n">
-        <v>648</v>
+        <v>1059</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>934</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6761</v>
+        <v>6219</v>
       </c>
       <c r="C2" t="n">
-        <v>14724</v>
+        <v>6133</v>
       </c>
       <c r="D2" t="n">
-        <v>24410</v>
+        <v>32466</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3624</v>
+        <v>3184</v>
       </c>
       <c r="C3" t="n">
-        <v>7085</v>
+        <v>5432</v>
       </c>
       <c r="D3" t="n">
-        <v>7742</v>
+        <v>14731</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2087</v>
+        <v>1598</v>
       </c>
       <c r="C4" t="n">
-        <v>3599</v>
+        <v>4211</v>
       </c>
       <c r="D4" t="n">
-        <v>2747</v>
+        <v>4837</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>978</v>
+        <v>806</v>
       </c>
       <c r="C5" t="n">
-        <v>2179</v>
+        <v>2626</v>
       </c>
       <c r="D5" t="n">
-        <v>1224</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>331</v>
+        <v>275</v>
       </c>
       <c r="C6" t="n">
-        <v>777</v>
+        <v>1335</v>
       </c>
       <c r="D6" t="n">
-        <v>772</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>320</v>
+        <v>442</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5899</v>
+        <v>4711</v>
       </c>
       <c r="C2" t="n">
-        <v>9899</v>
+        <v>4696</v>
       </c>
       <c r="D2" t="n">
-        <v>26105</v>
+        <v>34277</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4317</v>
+        <v>3916</v>
       </c>
       <c r="C3" t="n">
-        <v>9987</v>
+        <v>5023</v>
       </c>
       <c r="D3" t="n">
-        <v>10093</v>
+        <v>16626</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2507</v>
+        <v>2064</v>
       </c>
       <c r="C4" t="n">
-        <v>5665</v>
+        <v>4850</v>
       </c>
       <c r="D4" t="n">
-        <v>3718</v>
+        <v>6684</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1358</v>
+        <v>1068</v>
       </c>
       <c r="C5" t="n">
-        <v>2978</v>
+        <v>3484</v>
       </c>
       <c r="D5" t="n">
-        <v>1493</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>610</v>
+        <v>492</v>
       </c>
       <c r="C6" t="n">
-        <v>1574</v>
+        <v>2037</v>
       </c>
       <c r="D6" t="n">
-        <v>840</v>
+        <v>885</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="C7" t="n">
-        <v>579</v>
+        <v>931</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>277</v>
+        <v>335</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
         <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4595</v>
+        <v>4632</v>
       </c>
       <c r="C2" t="n">
-        <v>7069</v>
+        <v>4080</v>
       </c>
       <c r="D2" t="n">
-        <v>20480</v>
+        <v>29913</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4188</v>
+        <v>3543</v>
       </c>
       <c r="C3" t="n">
-        <v>8603</v>
+        <v>4214</v>
       </c>
       <c r="D3" t="n">
-        <v>11928</v>
+        <v>18138</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2934</v>
+        <v>2551</v>
       </c>
       <c r="C4" t="n">
-        <v>7995</v>
+        <v>4843</v>
       </c>
       <c r="D4" t="n">
-        <v>4828</v>
+        <v>8230</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1681</v>
+        <v>1351</v>
       </c>
       <c r="C5" t="n">
-        <v>4386</v>
+        <v>4099</v>
       </c>
       <c r="D5" t="n">
-        <v>1839</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>892</v>
+        <v>703</v>
       </c>
       <c r="C6" t="n">
-        <v>2281</v>
+        <v>2764</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>349</v>
+        <v>282</v>
       </c>
       <c r="C7" t="n">
-        <v>1105</v>
+        <v>1494</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>430</v>
+        <v>623</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6507,10 +6507,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>157</v>
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_3_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_3_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5844</v>
+        <v>8205</v>
       </c>
       <c r="C2" t="n">
-        <v>9115</v>
+        <v>12455</v>
       </c>
       <c r="D2" t="n">
-        <v>33321</v>
+        <v>25117</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3320</v>
+        <v>4694</v>
       </c>
       <c r="C3" t="n">
-        <v>3631</v>
+        <v>5493</v>
       </c>
       <c r="D3" t="n">
-        <v>18585</v>
+        <v>15640</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2567</v>
+        <v>3290</v>
       </c>
       <c r="C4" t="n">
-        <v>4422</v>
+        <v>3800</v>
       </c>
       <c r="D4" t="n">
-        <v>9691</v>
+        <v>6985</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1671</v>
+        <v>2059</v>
       </c>
       <c r="C5" t="n">
-        <v>4338</v>
+        <v>2867</v>
       </c>
       <c r="D5" t="n">
-        <v>3599</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>901</v>
+        <v>1216</v>
       </c>
       <c r="C6" t="n">
-        <v>3376</v>
+        <v>1921</v>
       </c>
       <c r="D6" t="n">
-        <v>1338</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>421</v>
+        <v>631</v>
       </c>
       <c r="C7" t="n">
-        <v>2090</v>
+        <v>1056</v>
       </c>
       <c r="D7" t="n">
-        <v>669</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>244</v>
       </c>
       <c r="C8" t="n">
-        <v>1009</v>
+        <v>489</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C9" t="n">
-        <v>425</v>
+        <v>271</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6495</v>
+        <v>10791</v>
       </c>
       <c r="C2" t="n">
-        <v>11691</v>
+        <v>13910</v>
       </c>
       <c r="D2" t="n">
-        <v>34695</v>
+        <v>31203</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3567</v>
+        <v>5127</v>
       </c>
       <c r="C3" t="n">
-        <v>5312</v>
+        <v>7812</v>
       </c>
       <c r="D3" t="n">
-        <v>19252</v>
+        <v>15928</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2465</v>
+        <v>3385</v>
       </c>
       <c r="C4" t="n">
-        <v>3923</v>
+        <v>4529</v>
       </c>
       <c r="D4" t="n">
-        <v>10669</v>
+        <v>8268</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1810</v>
+        <v>2299</v>
       </c>
       <c r="C5" t="n">
-        <v>4285</v>
+        <v>3264</v>
       </c>
       <c r="D5" t="n">
-        <v>4425</v>
+        <v>3190</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1119</v>
+        <v>1454</v>
       </c>
       <c r="C6" t="n">
-        <v>3726</v>
+        <v>2327</v>
       </c>
       <c r="D6" t="n">
-        <v>1632</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>552</v>
+        <v>810</v>
       </c>
       <c r="C7" t="n">
-        <v>2643</v>
+        <v>1462</v>
       </c>
       <c r="D7" t="n">
-        <v>760</v>
+        <v>714</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>231</v>
+        <v>363</v>
       </c>
       <c r="C8" t="n">
-        <v>1443</v>
+        <v>739</v>
       </c>
       <c r="D8" t="n">
-        <v>453</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="C9" t="n">
-        <v>655</v>
+        <v>367</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>300</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6862</v>
+        <v>11350</v>
       </c>
       <c r="C2" t="n">
-        <v>11962</v>
+        <v>9564</v>
       </c>
       <c r="D2" t="n">
-        <v>39932</v>
+        <v>40788</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3837</v>
+        <v>6074</v>
       </c>
       <c r="C3" t="n">
-        <v>6970</v>
+        <v>9241</v>
       </c>
       <c r="D3" t="n">
-        <v>19873</v>
+        <v>16838</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2489</v>
+        <v>3506</v>
       </c>
       <c r="C4" t="n">
-        <v>4390</v>
+        <v>5947</v>
       </c>
       <c r="D4" t="n">
-        <v>11478</v>
+        <v>9113</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1838</v>
+        <v>2463</v>
       </c>
       <c r="C5" t="n">
-        <v>4046</v>
+        <v>3723</v>
       </c>
       <c r="D5" t="n">
-        <v>5189</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1261</v>
+        <v>1645</v>
       </c>
       <c r="C6" t="n">
-        <v>3877</v>
+        <v>2687</v>
       </c>
       <c r="D6" t="n">
-        <v>1970</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>688</v>
+        <v>970</v>
       </c>
       <c r="C7" t="n">
-        <v>3040</v>
+        <v>1834</v>
       </c>
       <c r="D7" t="n">
-        <v>871</v>
+        <v>795</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>310</v>
+        <v>483</v>
       </c>
       <c r="C8" t="n">
-        <v>1901</v>
+        <v>1029</v>
       </c>
       <c r="D8" t="n">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>197</v>
       </c>
       <c r="C9" t="n">
-        <v>934</v>
+        <v>516</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>422</v>
+        <v>280</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6379</v>
+        <v>10336</v>
       </c>
       <c r="C2" t="n">
-        <v>8325</v>
+        <v>6350</v>
       </c>
       <c r="D2" t="n">
-        <v>32899</v>
+        <v>32950</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4507</v>
+        <v>6920</v>
       </c>
       <c r="C3" t="n">
-        <v>9789</v>
+        <v>12455</v>
       </c>
       <c r="D3" t="n">
-        <v>21650</v>
+        <v>18556</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1698</v>
+        <v>2275</v>
       </c>
       <c r="C4" t="n">
-        <v>6244</v>
+        <v>6999</v>
       </c>
       <c r="D4" t="n">
-        <v>11079</v>
+        <v>8676</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1165</v>
+        <v>1519</v>
       </c>
       <c r="C5" t="n">
-        <v>3799</v>
+        <v>2633</v>
       </c>
       <c r="D5" t="n">
-        <v>3325</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>635</v>
+        <v>896</v>
       </c>
       <c r="C6" t="n">
-        <v>2979</v>
+        <v>1797</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>779</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>286</v>
+        <v>446</v>
       </c>
       <c r="C7" t="n">
-        <v>1862</v>
+        <v>1008</v>
       </c>
       <c r="D7" t="n">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>182</v>
       </c>
       <c r="C8" t="n">
-        <v>915</v>
+        <v>505</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3870</v>
+        <v>6229</v>
       </c>
       <c r="C2" t="n">
-        <v>4400</v>
+        <v>2779</v>
       </c>
       <c r="D2" t="n">
-        <v>22398</v>
+        <v>22247</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4563</v>
+        <v>7246</v>
       </c>
       <c r="C3" t="n">
-        <v>8310</v>
+        <v>8670</v>
       </c>
       <c r="D3" t="n">
-        <v>22140</v>
+        <v>19708</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2366</v>
+        <v>3556</v>
       </c>
       <c r="C4" t="n">
-        <v>7953</v>
+        <v>9741</v>
       </c>
       <c r="D4" t="n">
-        <v>12370</v>
+        <v>10096</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1294</v>
+        <v>1696</v>
       </c>
       <c r="C5" t="n">
-        <v>4828</v>
+        <v>4548</v>
       </c>
       <c r="D5" t="n">
-        <v>4287</v>
+        <v>3333</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>747</v>
+        <v>1079</v>
       </c>
       <c r="C6" t="n">
-        <v>3436</v>
+        <v>2185</v>
       </c>
       <c r="D6" t="n">
-        <v>1081</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>269</v>
+        <v>426</v>
       </c>
       <c r="C7" t="n">
-        <v>2291</v>
+        <v>1320</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="C8" t="n">
-        <v>1207</v>
+        <v>664</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>447</v>
+        <v>329</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4655</v>
+        <v>6940</v>
       </c>
       <c r="C2" t="n">
-        <v>10773</v>
+        <v>3921</v>
       </c>
       <c r="D2" t="n">
-        <v>20868</v>
+        <v>19402</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3632</v>
+        <v>5711</v>
       </c>
       <c r="C3" t="n">
-        <v>5748</v>
+        <v>5090</v>
       </c>
       <c r="D3" t="n">
-        <v>20687</v>
+        <v>18717</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2804</v>
+        <v>4472</v>
       </c>
       <c r="C4" t="n">
-        <v>7958</v>
+        <v>9086</v>
       </c>
       <c r="D4" t="n">
-        <v>13588</v>
+        <v>11450</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1543</v>
+        <v>2199</v>
       </c>
       <c r="C5" t="n">
-        <v>6213</v>
+        <v>6946</v>
       </c>
       <c r="D5" t="n">
-        <v>5398</v>
+        <v>4335</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>887</v>
+        <v>1237</v>
       </c>
       <c r="C6" t="n">
-        <v>4005</v>
+        <v>3273</v>
       </c>
       <c r="D6" t="n">
-        <v>1528</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>399</v>
+        <v>614</v>
       </c>
       <c r="C7" t="n">
-        <v>2795</v>
+        <v>1713</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>221</v>
       </c>
       <c r="C8" t="n">
-        <v>1643</v>
+        <v>940</v>
       </c>
       <c r="D8" t="n">
-        <v>351</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>726</v>
+        <v>460</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
         <v>102</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2775</v>
+        <v>4087</v>
       </c>
       <c r="C2" t="n">
-        <v>5132</v>
+        <v>1845</v>
       </c>
       <c r="D2" t="n">
-        <v>14539</v>
+        <v>13389</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3734</v>
+        <v>5801</v>
       </c>
       <c r="C3" t="n">
-        <v>7230</v>
+        <v>4524</v>
       </c>
       <c r="D3" t="n">
-        <v>20242</v>
+        <v>18344</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3090</v>
+        <v>4926</v>
       </c>
       <c r="C4" t="n">
-        <v>7856</v>
+        <v>8426</v>
       </c>
       <c r="D4" t="n">
-        <v>14492</v>
+        <v>12349</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1593</v>
+        <v>2274</v>
       </c>
       <c r="C5" t="n">
-        <v>7604</v>
+        <v>8335</v>
       </c>
       <c r="D5" t="n">
-        <v>5686</v>
+        <v>4743</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>721</v>
+        <v>1081</v>
       </c>
       <c r="C6" t="n">
-        <v>4792</v>
+        <v>4066</v>
       </c>
       <c r="D6" t="n">
-        <v>1477</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>2962</v>
+        <v>1784</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>1194</v>
+        <v>745</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>257</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3323</v>
+        <v>5652</v>
       </c>
       <c r="C2" t="n">
-        <v>9054</v>
+        <v>2864</v>
       </c>
       <c r="D2" t="n">
-        <v>14949</v>
+        <v>17415</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2860</v>
+        <v>4338</v>
       </c>
       <c r="C3" t="n">
-        <v>5620</v>
+        <v>2924</v>
       </c>
       <c r="D3" t="n">
-        <v>18184</v>
+        <v>16437</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2920</v>
+        <v>4663</v>
       </c>
       <c r="C4" t="n">
-        <v>7479</v>
+        <v>6458</v>
       </c>
       <c r="D4" t="n">
-        <v>14934</v>
+        <v>12951</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1937</v>
+        <v>2939</v>
       </c>
       <c r="C5" t="n">
-        <v>7627</v>
+        <v>8202</v>
       </c>
       <c r="D5" t="n">
-        <v>6781</v>
+        <v>5812</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>949</v>
+        <v>1391</v>
       </c>
       <c r="C6" t="n">
-        <v>5930</v>
+        <v>5951</v>
       </c>
       <c r="D6" t="n">
-        <v>2037</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>265</v>
+        <v>426</v>
       </c>
       <c r="C7" t="n">
-        <v>3689</v>
+        <v>2717</v>
       </c>
       <c r="D7" t="n">
-        <v>683</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>1840</v>
+        <v>1153</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>589</v>
+        <v>419</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2188</v>
+        <v>4070</v>
       </c>
       <c r="C2" t="n">
-        <v>5178</v>
+        <v>2182</v>
       </c>
       <c r="D2" t="n">
-        <v>12136</v>
+        <v>13780</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2633</v>
+        <v>4177</v>
       </c>
       <c r="C3" t="n">
-        <v>6297</v>
+        <v>2631</v>
       </c>
       <c r="D3" t="n">
-        <v>16861</v>
+        <v>15660</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2672</v>
+        <v>4204</v>
       </c>
       <c r="C4" t="n">
-        <v>6807</v>
+        <v>5050</v>
       </c>
       <c r="D4" t="n">
-        <v>15028</v>
+        <v>13150</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2097</v>
+        <v>3276</v>
       </c>
       <c r="C5" t="n">
         <v>7710</v>
       </c>
       <c r="D5" t="n">
-        <v>7566</v>
+        <v>6569</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1113</v>
+        <v>1656</v>
       </c>
       <c r="C6" t="n">
-        <v>6671</v>
+        <v>6893</v>
       </c>
       <c r="D6" t="n">
-        <v>2417</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>238</v>
+        <v>396</v>
       </c>
       <c r="C7" t="n">
-        <v>4409</v>
+        <v>3694</v>
       </c>
       <c r="D7" t="n">
-        <v>774</v>
+        <v>769</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>2326</v>
+        <v>1515</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>646</v>
+        <v>494</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2418</v>
+        <v>6216</v>
       </c>
       <c r="C2" t="n">
-        <v>7832</v>
+        <v>6300</v>
       </c>
       <c r="D2" t="n">
-        <v>13925</v>
+        <v>17656</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2088</v>
+        <v>3482</v>
       </c>
       <c r="C3" t="n">
-        <v>5226</v>
+        <v>2174</v>
       </c>
       <c r="D3" t="n">
-        <v>15376</v>
+        <v>14432</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2333</v>
+        <v>3645</v>
       </c>
       <c r="C4" t="n">
-        <v>6454</v>
+        <v>3899</v>
       </c>
       <c r="D4" t="n">
-        <v>14673</v>
+        <v>13111</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2084</v>
+        <v>3276</v>
       </c>
       <c r="C5" t="n">
-        <v>7194</v>
+        <v>6451</v>
       </c>
       <c r="D5" t="n">
-        <v>8338</v>
+        <v>7190</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1332</v>
+        <v>2055</v>
       </c>
       <c r="C6" t="n">
-        <v>7005</v>
+        <v>7155</v>
       </c>
       <c r="D6" t="n">
-        <v>3028</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>444</v>
+        <v>714</v>
       </c>
       <c r="C7" t="n">
-        <v>5270</v>
+        <v>4951</v>
       </c>
       <c r="D7" t="n">
-        <v>959</v>
+        <v>930</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="C8" t="n">
-        <v>3019</v>
+        <v>2283</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>1178</v>
+        <v>838</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>344</v>
+        <v>308</v>
       </c>
       <c r="D10" t="n">
         <v>187</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4856</v>
+        <v>8460</v>
       </c>
       <c r="C2" t="n">
-        <v>10732</v>
+        <v>2889</v>
       </c>
       <c r="D2" t="n">
-        <v>11743</v>
+        <v>7677</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1749</v>
+        <v>4449</v>
       </c>
       <c r="C2" t="n">
-        <v>4573</v>
+        <v>3579</v>
       </c>
       <c r="D2" t="n">
-        <v>10360</v>
+        <v>12995</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2747</v>
+        <v>4662</v>
       </c>
       <c r="C3" t="n">
-        <v>6257</v>
+        <v>3319</v>
       </c>
       <c r="D3" t="n">
-        <v>16526</v>
+        <v>15865</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3099</v>
+        <v>4892</v>
       </c>
       <c r="C4" t="n">
-        <v>8995</v>
+        <v>5954</v>
       </c>
       <c r="D4" t="n">
-        <v>15101</v>
+        <v>13362</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1269</v>
+        <v>1989</v>
       </c>
       <c r="C5" t="n">
-        <v>10187</v>
+        <v>9820</v>
       </c>
       <c r="D5" t="n">
-        <v>7516</v>
+        <v>6554</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>410</v>
+        <v>659</v>
       </c>
       <c r="C6" t="n">
-        <v>6400</v>
+        <v>6254</v>
       </c>
       <c r="D6" t="n">
-        <v>2271</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>2958</v>
+        <v>2237</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>1154</v>
+        <v>821</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>337</v>
+        <v>301</v>
       </c>
       <c r="D9" t="n">
         <v>183</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6650</v>
+        <v>7986</v>
       </c>
       <c r="C2" t="n">
-        <v>5966</v>
+        <v>2990</v>
       </c>
       <c r="D2" t="n">
-        <v>23791</v>
+        <v>13486</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2064</v>
+        <v>3592</v>
       </c>
       <c r="C3" t="n">
-        <v>5408</v>
+        <v>1456</v>
       </c>
       <c r="D3" t="n">
-        <v>2612</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4350</v>
+        <v>4914</v>
       </c>
       <c r="C2" t="n">
-        <v>5738</v>
+        <v>3381</v>
       </c>
       <c r="D2" t="n">
-        <v>36720</v>
+        <v>18572</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3574</v>
+        <v>4757</v>
       </c>
       <c r="C3" t="n">
-        <v>4936</v>
+        <v>2014</v>
       </c>
       <c r="D3" t="n">
-        <v>5977</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>931</v>
+        <v>1594</v>
       </c>
       <c r="C4" t="n">
-        <v>3212</v>
+        <v>910</v>
       </c>
       <c r="D4" t="n">
-        <v>1707</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4189</v>
+        <v>4746</v>
       </c>
       <c r="C2" t="n">
-        <v>8750</v>
+        <v>6586</v>
       </c>
       <c r="D2" t="n">
-        <v>36812</v>
+        <v>21678</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3253</v>
+        <v>4032</v>
       </c>
       <c r="C3" t="n">
-        <v>4652</v>
+        <v>2388</v>
       </c>
       <c r="D3" t="n">
-        <v>10465</v>
+        <v>5834</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1882</v>
+        <v>2692</v>
       </c>
       <c r="C4" t="n">
-        <v>4105</v>
+        <v>1507</v>
       </c>
       <c r="D4" t="n">
-        <v>2474</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>436</v>
+        <v>714</v>
       </c>
       <c r="C5" t="n">
-        <v>1823</v>
+        <v>599</v>
       </c>
       <c r="D5" t="n">
-        <v>1254</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5903</v>
+        <v>6390</v>
       </c>
       <c r="C2" t="n">
-        <v>7391</v>
+        <v>3857</v>
       </c>
       <c r="D2" t="n">
-        <v>32754</v>
+        <v>18987</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3038</v>
+        <v>3605</v>
       </c>
       <c r="C3" t="n">
-        <v>5859</v>
+        <v>3988</v>
       </c>
       <c r="D3" t="n">
-        <v>13733</v>
+        <v>7831</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2172</v>
+        <v>2853</v>
       </c>
       <c r="C4" t="n">
-        <v>4308</v>
+        <v>1957</v>
       </c>
       <c r="D4" t="n">
-        <v>3856</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>935</v>
+        <v>1424</v>
       </c>
       <c r="C5" t="n">
-        <v>2928</v>
+        <v>1060</v>
       </c>
       <c r="D5" t="n">
-        <v>1426</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>367</v>
       </c>
       <c r="C6" t="n">
-        <v>1059</v>
+        <v>453</v>
       </c>
       <c r="D6" t="n">
-        <v>934</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6219</v>
+        <v>6928</v>
       </c>
       <c r="C2" t="n">
-        <v>6133</v>
+        <v>5158</v>
       </c>
       <c r="D2" t="n">
-        <v>32466</v>
+        <v>35903</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3184</v>
+        <v>3622</v>
       </c>
       <c r="C3" t="n">
-        <v>5432</v>
+        <v>3208</v>
       </c>
       <c r="D3" t="n">
-        <v>14731</v>
+        <v>8444</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1598</v>
+        <v>2003</v>
       </c>
       <c r="C4" t="n">
-        <v>4211</v>
+        <v>2525</v>
       </c>
       <c r="D4" t="n">
-        <v>4837</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>806</v>
+        <v>1138</v>
       </c>
       <c r="C5" t="n">
-        <v>2626</v>
+        <v>1129</v>
       </c>
       <c r="D5" t="n">
-        <v>1459</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>275</v>
+        <v>425</v>
       </c>
       <c r="C6" t="n">
-        <v>1335</v>
+        <v>515</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>442</v>
+        <v>256</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5986,7 +5986,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4711</v>
+        <v>7188</v>
       </c>
       <c r="C2" t="n">
-        <v>4696</v>
+        <v>5943</v>
       </c>
       <c r="D2" t="n">
-        <v>34277</v>
+        <v>27332</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3916</v>
+        <v>4412</v>
       </c>
       <c r="C3" t="n">
-        <v>5023</v>
+        <v>3760</v>
       </c>
       <c r="D3" t="n">
-        <v>16626</v>
+        <v>12641</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2064</v>
+        <v>2485</v>
       </c>
       <c r="C4" t="n">
-        <v>4850</v>
+        <v>2898</v>
       </c>
       <c r="D4" t="n">
-        <v>6684</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1068</v>
+        <v>1402</v>
       </c>
       <c r="C5" t="n">
-        <v>3484</v>
+        <v>1949</v>
       </c>
       <c r="D5" t="n">
-        <v>2049</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>492</v>
+        <v>736</v>
       </c>
       <c r="C6" t="n">
-        <v>2037</v>
+        <v>868</v>
       </c>
       <c r="D6" t="n">
-        <v>885</v>
+        <v>836</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>246</v>
       </c>
       <c r="C7" t="n">
-        <v>931</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>335</v>
+        <v>241</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
         <v>197</v>
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4632</v>
+        <v>6751</v>
       </c>
       <c r="C2" t="n">
-        <v>4080</v>
+        <v>8148</v>
       </c>
       <c r="D2" t="n">
-        <v>29913</v>
+        <v>30367</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3543</v>
+        <v>4774</v>
       </c>
       <c r="C3" t="n">
-        <v>4214</v>
+        <v>4307</v>
       </c>
       <c r="D3" t="n">
-        <v>18138</v>
+        <v>14178</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2551</v>
+        <v>2996</v>
       </c>
       <c r="C4" t="n">
-        <v>4843</v>
+        <v>3342</v>
       </c>
       <c r="D4" t="n">
-        <v>8230</v>
+        <v>5658</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1351</v>
+        <v>1711</v>
       </c>
       <c r="C5" t="n">
-        <v>4099</v>
+        <v>2445</v>
       </c>
       <c r="D5" t="n">
-        <v>2832</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>703</v>
+        <v>989</v>
       </c>
       <c r="C6" t="n">
-        <v>2764</v>
+        <v>1440</v>
       </c>
       <c r="D6" t="n">
-        <v>1065</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>282</v>
+        <v>437</v>
       </c>
       <c r="C7" t="n">
-        <v>1494</v>
+        <v>658</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="C8" t="n">
-        <v>623</v>
+        <v>327</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_3_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_3_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8205</v>
+        <v>1605</v>
       </c>
       <c r="C2" t="n">
-        <v>12455</v>
+        <v>2514</v>
       </c>
       <c r="D2" t="n">
-        <v>25117</v>
+        <v>21167</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4694</v>
+        <v>2520</v>
       </c>
       <c r="C3" t="n">
-        <v>5493</v>
+        <v>6299</v>
       </c>
       <c r="D3" t="n">
-        <v>15640</v>
+        <v>14895</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3290</v>
+        <v>1472</v>
       </c>
       <c r="C4" t="n">
-        <v>3800</v>
+        <v>7726</v>
       </c>
       <c r="D4" t="n">
-        <v>6985</v>
+        <v>5423</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2059</v>
+        <v>743</v>
       </c>
       <c r="C5" t="n">
-        <v>2867</v>
+        <v>4809</v>
       </c>
       <c r="D5" t="n">
-        <v>2574</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1216</v>
+        <v>313</v>
       </c>
       <c r="C6" t="n">
-        <v>1921</v>
+        <v>1886</v>
       </c>
       <c r="D6" t="n">
-        <v>1094</v>
+        <v>729</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>631</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>1056</v>
+        <v>706</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>244</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>489</v>
+        <v>347</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>39</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10791</v>
+        <v>1413</v>
       </c>
       <c r="C2" t="n">
-        <v>13910</v>
+        <v>5420</v>
       </c>
       <c r="D2" t="n">
-        <v>31203</v>
+        <v>20109</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5127</v>
+        <v>1775</v>
       </c>
       <c r="C3" t="n">
-        <v>7812</v>
+        <v>3766</v>
       </c>
       <c r="D3" t="n">
-        <v>15928</v>
+        <v>14799</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3385</v>
+        <v>1702</v>
       </c>
       <c r="C4" t="n">
-        <v>4529</v>
+        <v>6858</v>
       </c>
       <c r="D4" t="n">
-        <v>8268</v>
+        <v>6985</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2299</v>
+        <v>951</v>
       </c>
       <c r="C5" t="n">
-        <v>3264</v>
+        <v>6221</v>
       </c>
       <c r="D5" t="n">
-        <v>3190</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1454</v>
+        <v>456</v>
       </c>
       <c r="C6" t="n">
-        <v>2327</v>
+        <v>3343</v>
       </c>
       <c r="D6" t="n">
-        <v>1320</v>
+        <v>902</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>810</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>1462</v>
+        <v>1279</v>
       </c>
       <c r="D7" t="n">
-        <v>714</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>363</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>739</v>
+        <v>512</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>367</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11350</v>
+        <v>749</v>
       </c>
       <c r="C2" t="n">
-        <v>9564</v>
+        <v>2230</v>
       </c>
       <c r="D2" t="n">
-        <v>40788</v>
+        <v>13540</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6074</v>
+        <v>1609</v>
       </c>
       <c r="C3" t="n">
-        <v>9241</v>
+        <v>4257</v>
       </c>
       <c r="D3" t="n">
-        <v>16838</v>
+        <v>15076</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3506</v>
+        <v>1869</v>
       </c>
       <c r="C4" t="n">
-        <v>5947</v>
+        <v>6222</v>
       </c>
       <c r="D4" t="n">
-        <v>9113</v>
+        <v>8075</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2463</v>
+        <v>961</v>
       </c>
       <c r="C5" t="n">
-        <v>3723</v>
+        <v>7158</v>
       </c>
       <c r="D5" t="n">
-        <v>3873</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1645</v>
+        <v>365</v>
       </c>
       <c r="C6" t="n">
-        <v>2687</v>
+        <v>4271</v>
       </c>
       <c r="D6" t="n">
-        <v>1558</v>
+        <v>922</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>970</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>1834</v>
+        <v>1236</v>
       </c>
       <c r="D7" t="n">
-        <v>795</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>483</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1029</v>
+        <v>491</v>
       </c>
       <c r="D8" t="n">
-        <v>490</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>197</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>516</v>
+        <v>240</v>
       </c>
       <c r="D9" t="n">
-        <v>338</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>259</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>131</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10336</v>
+        <v>607</v>
       </c>
       <c r="C2" t="n">
-        <v>6350</v>
+        <v>3824</v>
       </c>
       <c r="D2" t="n">
-        <v>32950</v>
+        <v>10392</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6920</v>
+        <v>1043</v>
       </c>
       <c r="C3" t="n">
-        <v>12455</v>
+        <v>2838</v>
       </c>
       <c r="D3" t="n">
-        <v>18556</v>
+        <v>13925</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2275</v>
+        <v>1558</v>
       </c>
       <c r="C4" t="n">
-        <v>6999</v>
+        <v>5114</v>
       </c>
       <c r="D4" t="n">
-        <v>8676</v>
+        <v>9039</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1519</v>
+        <v>1205</v>
       </c>
       <c r="C5" t="n">
-        <v>2633</v>
+        <v>6610</v>
       </c>
       <c r="D5" t="n">
-        <v>2605</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>896</v>
+        <v>552</v>
       </c>
       <c r="C6" t="n">
-        <v>1797</v>
+        <v>5669</v>
       </c>
       <c r="D6" t="n">
-        <v>779</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>446</v>
+        <v>155</v>
       </c>
       <c r="C7" t="n">
-        <v>1008</v>
+        <v>2598</v>
       </c>
       <c r="D7" t="n">
-        <v>480</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>182</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>505</v>
+        <v>799</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>337</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6229</v>
+        <v>407</v>
       </c>
       <c r="C2" t="n">
-        <v>2779</v>
+        <v>1953</v>
       </c>
       <c r="D2" t="n">
-        <v>22247</v>
+        <v>7296</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7246</v>
+        <v>771</v>
       </c>
       <c r="C3" t="n">
-        <v>8670</v>
+        <v>2949</v>
       </c>
       <c r="D3" t="n">
-        <v>19708</v>
+        <v>12642</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3556</v>
+        <v>1280</v>
       </c>
       <c r="C4" t="n">
-        <v>9741</v>
+        <v>4084</v>
       </c>
       <c r="D4" t="n">
-        <v>10096</v>
+        <v>9601</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1696</v>
+        <v>1271</v>
       </c>
       <c r="C5" t="n">
-        <v>4548</v>
+        <v>6094</v>
       </c>
       <c r="D5" t="n">
-        <v>3333</v>
+        <v>4220</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1079</v>
+        <v>690</v>
       </c>
       <c r="C6" t="n">
-        <v>2185</v>
+        <v>6300</v>
       </c>
       <c r="D6" t="n">
-        <v>967</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>426</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>1320</v>
+        <v>3678</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>664</v>
+        <v>1247</v>
       </c>
       <c r="D8" t="n">
-        <v>346</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>329</v>
+        <v>438</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6940</v>
+        <v>1252</v>
       </c>
       <c r="C2" t="n">
-        <v>3921</v>
+        <v>9406</v>
       </c>
       <c r="D2" t="n">
-        <v>19402</v>
+        <v>10848</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5711</v>
+        <v>524</v>
       </c>
       <c r="C3" t="n">
-        <v>5090</v>
+        <v>2184</v>
       </c>
       <c r="D3" t="n">
-        <v>18717</v>
+        <v>11065</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4472</v>
+        <v>934</v>
       </c>
       <c r="C4" t="n">
-        <v>9086</v>
+        <v>3482</v>
       </c>
       <c r="D4" t="n">
-        <v>11450</v>
+        <v>9805</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2199</v>
+        <v>1176</v>
       </c>
       <c r="C5" t="n">
-        <v>6946</v>
+        <v>5041</v>
       </c>
       <c r="D5" t="n">
-        <v>4335</v>
+        <v>4918</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1237</v>
+        <v>849</v>
       </c>
       <c r="C6" t="n">
-        <v>3273</v>
+        <v>6148</v>
       </c>
       <c r="D6" t="n">
-        <v>1317</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>614</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>1713</v>
+        <v>4843</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>759</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>940</v>
+        <v>2235</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>460</v>
+        <v>743</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4087</v>
+        <v>841</v>
       </c>
       <c r="C2" t="n">
-        <v>1845</v>
+        <v>4891</v>
       </c>
       <c r="D2" t="n">
-        <v>13389</v>
+        <v>7810</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5801</v>
+        <v>861</v>
       </c>
       <c r="C3" t="n">
-        <v>4524</v>
+        <v>4373</v>
       </c>
       <c r="D3" t="n">
-        <v>18344</v>
+        <v>11960</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4926</v>
+        <v>1540</v>
       </c>
       <c r="C4" t="n">
-        <v>8426</v>
+        <v>5005</v>
       </c>
       <c r="D4" t="n">
-        <v>12349</v>
+        <v>10028</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2274</v>
+        <v>871</v>
       </c>
       <c r="C5" t="n">
-        <v>8335</v>
+        <v>8051</v>
       </c>
       <c r="D5" t="n">
-        <v>4743</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1081</v>
+        <v>299</v>
       </c>
       <c r="C6" t="n">
-        <v>4066</v>
+        <v>6252</v>
       </c>
       <c r="D6" t="n">
-        <v>1285</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>204</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>1784</v>
+        <v>2190</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>745</v>
+        <v>728</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5652</v>
+        <v>400</v>
       </c>
       <c r="C2" t="n">
-        <v>2864</v>
+        <v>3569</v>
       </c>
       <c r="D2" t="n">
-        <v>17415</v>
+        <v>5809</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4338</v>
+        <v>722</v>
       </c>
       <c r="C3" t="n">
-        <v>2924</v>
+        <v>4074</v>
       </c>
       <c r="D3" t="n">
-        <v>16437</v>
+        <v>10505</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4663</v>
+        <v>1026</v>
       </c>
       <c r="C4" t="n">
-        <v>6458</v>
+        <v>4399</v>
       </c>
       <c r="D4" t="n">
-        <v>12951</v>
+        <v>9644</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2939</v>
+        <v>822</v>
       </c>
       <c r="C5" t="n">
-        <v>8202</v>
+        <v>5859</v>
       </c>
       <c r="D5" t="n">
-        <v>5812</v>
+        <v>4734</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1391</v>
+        <v>303</v>
       </c>
       <c r="C6" t="n">
-        <v>5951</v>
+        <v>5844</v>
       </c>
       <c r="D6" t="n">
-        <v>1733</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>426</v>
+        <v>66</v>
       </c>
       <c r="C7" t="n">
-        <v>2717</v>
+        <v>2833</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1153</v>
+        <v>840</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>419</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4070</v>
+        <v>594</v>
       </c>
       <c r="C2" t="n">
-        <v>2182</v>
+        <v>4367</v>
       </c>
       <c r="D2" t="n">
-        <v>13780</v>
+        <v>10076</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4177</v>
+        <v>476</v>
       </c>
       <c r="C3" t="n">
-        <v>2631</v>
+        <v>3288</v>
       </c>
       <c r="D3" t="n">
-        <v>15660</v>
+        <v>8997</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4204</v>
+        <v>767</v>
       </c>
       <c r="C4" t="n">
-        <v>5050</v>
+        <v>4165</v>
       </c>
       <c r="D4" t="n">
-        <v>13150</v>
+        <v>9516</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3276</v>
+        <v>835</v>
       </c>
       <c r="C5" t="n">
-        <v>7710</v>
+        <v>4952</v>
       </c>
       <c r="D5" t="n">
-        <v>6569</v>
+        <v>5485</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1656</v>
+        <v>494</v>
       </c>
       <c r="C6" t="n">
-        <v>6893</v>
+        <v>5843</v>
       </c>
       <c r="D6" t="n">
-        <v>2098</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>396</v>
+        <v>151</v>
       </c>
       <c r="C7" t="n">
-        <v>3694</v>
+        <v>4336</v>
       </c>
       <c r="D7" t="n">
-        <v>769</v>
+        <v>755</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>1515</v>
+        <v>1804</v>
       </c>
       <c r="D8" t="n">
-        <v>421</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>494</v>
+        <v>537</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6216</v>
+        <v>354</v>
       </c>
       <c r="C2" t="n">
-        <v>6300</v>
+        <v>6145</v>
       </c>
       <c r="D2" t="n">
-        <v>17656</v>
+        <v>13719</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3482</v>
+        <v>436</v>
       </c>
       <c r="C3" t="n">
-        <v>2174</v>
+        <v>3338</v>
       </c>
       <c r="D3" t="n">
-        <v>14432</v>
+        <v>8533</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3645</v>
+        <v>554</v>
       </c>
       <c r="C4" t="n">
-        <v>3899</v>
+        <v>3623</v>
       </c>
       <c r="D4" t="n">
-        <v>13111</v>
+        <v>9045</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3276</v>
+        <v>736</v>
       </c>
       <c r="C5" t="n">
-        <v>6451</v>
+        <v>4456</v>
       </c>
       <c r="D5" t="n">
-        <v>7190</v>
+        <v>6014</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2055</v>
+        <v>594</v>
       </c>
       <c r="C6" t="n">
-        <v>7155</v>
+        <v>5354</v>
       </c>
       <c r="D6" t="n">
-        <v>2671</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>714</v>
+        <v>264</v>
       </c>
       <c r="C7" t="n">
-        <v>4951</v>
+        <v>5043</v>
       </c>
       <c r="D7" t="n">
-        <v>930</v>
+        <v>967</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>2283</v>
+        <v>2927</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>838</v>
+        <v>1095</v>
       </c>
       <c r="D9" t="n">
-        <v>313</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8460</v>
+        <v>5105</v>
       </c>
       <c r="C2" t="n">
-        <v>2889</v>
+        <v>8812</v>
       </c>
       <c r="D2" t="n">
-        <v>7677</v>
+        <v>12504</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4449</v>
+        <v>1211</v>
       </c>
       <c r="C2" t="n">
-        <v>3579</v>
+        <v>10177</v>
       </c>
       <c r="D2" t="n">
-        <v>12995</v>
+        <v>13096</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4662</v>
+        <v>335</v>
       </c>
       <c r="C3" t="n">
-        <v>3319</v>
+        <v>4043</v>
       </c>
       <c r="D3" t="n">
-        <v>15865</v>
+        <v>8664</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4892</v>
+        <v>440</v>
       </c>
       <c r="C4" t="n">
-        <v>5954</v>
+        <v>3378</v>
       </c>
       <c r="D4" t="n">
-        <v>13362</v>
+        <v>8686</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1989</v>
+        <v>605</v>
       </c>
       <c r="C5" t="n">
-        <v>9820</v>
+        <v>3979</v>
       </c>
       <c r="D5" t="n">
-        <v>6554</v>
+        <v>6239</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>659</v>
+        <v>609</v>
       </c>
       <c r="C6" t="n">
-        <v>6254</v>
+        <v>4906</v>
       </c>
       <c r="D6" t="n">
-        <v>2101</v>
+        <v>3180</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>136</v>
+        <v>356</v>
       </c>
       <c r="C7" t="n">
-        <v>2237</v>
+        <v>5125</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>821</v>
+        <v>3817</v>
       </c>
       <c r="D8" t="n">
-        <v>306</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>1830</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
+        <v>623</v>
+      </c>
+      <c r="D10" t="n">
         <v>159</v>
-      </c>
-      <c r="D10" t="n">
-        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>62</v>
+      </c>
+      <c r="D13" t="n">
         <v>39</v>
-      </c>
-      <c r="D13" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7986</v>
+        <v>4963</v>
       </c>
       <c r="C2" t="n">
-        <v>2990</v>
+        <v>10163</v>
       </c>
       <c r="D2" t="n">
-        <v>13486</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3592</v>
+        <v>1686</v>
       </c>
       <c r="C3" t="n">
-        <v>1456</v>
+        <v>3479</v>
       </c>
       <c r="D3" t="n">
-        <v>1929</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4914</v>
+        <v>2966</v>
       </c>
       <c r="C2" t="n">
-        <v>3381</v>
+        <v>4958</v>
       </c>
       <c r="D2" t="n">
-        <v>18572</v>
+        <v>15033</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4757</v>
+        <v>2804</v>
       </c>
       <c r="C3" t="n">
-        <v>2014</v>
+        <v>6453</v>
       </c>
       <c r="D3" t="n">
-        <v>3728</v>
+        <v>4377</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1594</v>
+        <v>805</v>
       </c>
       <c r="C4" t="n">
-        <v>910</v>
+        <v>2218</v>
       </c>
       <c r="D4" t="n">
-        <v>1570</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>327</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4746</v>
+        <v>2447</v>
       </c>
       <c r="C2" t="n">
-        <v>6586</v>
+        <v>6863</v>
       </c>
       <c r="D2" t="n">
-        <v>21678</v>
+        <v>18612</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4032</v>
+        <v>2380</v>
       </c>
       <c r="C3" t="n">
-        <v>2388</v>
+        <v>4813</v>
       </c>
       <c r="D3" t="n">
-        <v>5834</v>
+        <v>5845</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2692</v>
+        <v>1585</v>
       </c>
       <c r="C4" t="n">
-        <v>1507</v>
+        <v>4692</v>
       </c>
       <c r="D4" t="n">
-        <v>1936</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>714</v>
+        <v>390</v>
       </c>
       <c r="C5" t="n">
-        <v>599</v>
+        <v>1360</v>
       </c>
       <c r="D5" t="n">
-        <v>1208</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6390</v>
+        <v>2927</v>
       </c>
       <c r="C2" t="n">
-        <v>3857</v>
+        <v>6556</v>
       </c>
       <c r="D2" t="n">
-        <v>18987</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3605</v>
+        <v>1992</v>
       </c>
       <c r="C3" t="n">
-        <v>3988</v>
+        <v>5188</v>
       </c>
       <c r="D3" t="n">
-        <v>7831</v>
+        <v>7466</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2853</v>
+        <v>1716</v>
       </c>
       <c r="C4" t="n">
-        <v>1957</v>
+        <v>4617</v>
       </c>
       <c r="D4" t="n">
-        <v>2569</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1424</v>
+        <v>842</v>
       </c>
       <c r="C5" t="n">
-        <v>1060</v>
+        <v>3186</v>
       </c>
       <c r="D5" t="n">
-        <v>1304</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>367</v>
+        <v>221</v>
       </c>
       <c r="C6" t="n">
-        <v>453</v>
+        <v>848</v>
       </c>
       <c r="D6" t="n">
-        <v>940</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6928</v>
+        <v>2256</v>
       </c>
       <c r="C2" t="n">
-        <v>5158</v>
+        <v>6000</v>
       </c>
       <c r="D2" t="n">
-        <v>35903</v>
+        <v>29294</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3622</v>
+        <v>2000</v>
       </c>
       <c r="C3" t="n">
-        <v>3208</v>
+        <v>5128</v>
       </c>
       <c r="D3" t="n">
-        <v>8444</v>
+        <v>8845</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2003</v>
+        <v>1601</v>
       </c>
       <c r="C4" t="n">
-        <v>2525</v>
+        <v>4827</v>
       </c>
       <c r="D4" t="n">
-        <v>2990</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1138</v>
+        <v>1093</v>
       </c>
       <c r="C5" t="n">
-        <v>1129</v>
+        <v>3830</v>
       </c>
       <c r="D5" t="n">
-        <v>1212</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>425</v>
+        <v>460</v>
       </c>
       <c r="C6" t="n">
-        <v>515</v>
+        <v>2028</v>
       </c>
       <c r="D6" t="n">
-        <v>755</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>256</v>
+        <v>571</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7188</v>
+        <v>3894</v>
       </c>
       <c r="C2" t="n">
-        <v>5943</v>
+        <v>9627</v>
       </c>
       <c r="D2" t="n">
-        <v>27332</v>
+        <v>40265</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4412</v>
+        <v>1748</v>
       </c>
       <c r="C3" t="n">
-        <v>3760</v>
+        <v>4857</v>
       </c>
       <c r="D3" t="n">
-        <v>12641</v>
+        <v>11181</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2485</v>
+        <v>1527</v>
       </c>
       <c r="C4" t="n">
-        <v>2898</v>
+        <v>4879</v>
       </c>
       <c r="D4" t="n">
-        <v>4050</v>
+        <v>4341</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1402</v>
+        <v>1182</v>
       </c>
       <c r="C5" t="n">
-        <v>1949</v>
+        <v>4238</v>
       </c>
       <c r="D5" t="n">
-        <v>1521</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>736</v>
+        <v>669</v>
       </c>
       <c r="C6" t="n">
-        <v>868</v>
+        <v>2835</v>
       </c>
       <c r="D6" t="n">
-        <v>836</v>
+        <v>976</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>1256</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>241</v>
+        <v>423</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6751</v>
+        <v>3398</v>
       </c>
       <c r="C2" t="n">
-        <v>8148</v>
+        <v>5930</v>
       </c>
       <c r="D2" t="n">
-        <v>30367</v>
+        <v>31460</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4774</v>
+        <v>2507</v>
       </c>
       <c r="C3" t="n">
-        <v>4307</v>
+        <v>8073</v>
       </c>
       <c r="D3" t="n">
-        <v>14178</v>
+        <v>12693</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2996</v>
+        <v>1092</v>
       </c>
       <c r="C4" t="n">
-        <v>3342</v>
+        <v>7112</v>
       </c>
       <c r="D4" t="n">
-        <v>5658</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1711</v>
+        <v>618</v>
       </c>
       <c r="C5" t="n">
-        <v>2445</v>
+        <v>2778</v>
       </c>
       <c r="D5" t="n">
-        <v>1960</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>989</v>
+        <v>231</v>
       </c>
       <c r="C6" t="n">
-        <v>1440</v>
+        <v>1230</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>630</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>437</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>658</v>
+        <v>414</v>
       </c>
       <c r="D7" t="n">
-        <v>608</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
         <v>160</v>
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>40</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
